--- a/max_amplitudes.xlsx
+++ b/max_amplitudes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B554"/>
+  <dimension ref="A1:B501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,4428 +442,4002 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>3.26702</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>362.638</v>
+        <v>31.62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>3.76</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>435.749</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>-0.529583</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>489.491</v>
+        <v>73.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>-1.02331</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>392.04</v>
+        <v>99.96000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>-0.467068</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>336.091</v>
+        <v>115.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>-1.9143</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>330.524</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>-2.35413</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>315.74</v>
+        <v>86.19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>-2.37848</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>341.443</v>
+        <v>60.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>1.67756</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>388.332</v>
+        <v>17.85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>3.94998</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>292.243</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>5.45254</v>
+        <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>364.503</v>
+        <v>62.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>-5.80924</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>416.597</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>3.37694</v>
+        <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>244.229</v>
+        <v>94.35000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>-0.08288959999999999</v>
+        <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>314.334</v>
+        <v>65.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>-0.0622864</v>
+        <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>308.709</v>
+        <v>85.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>3.98773</v>
+        <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>276.228</v>
+        <v>59.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>6.3448</v>
+        <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>338.6</v>
+        <v>86.19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>0.0481911</v>
+        <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>341.779</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>-4.06237</v>
+        <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>325.431</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>1.1073</v>
+        <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>389.318</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>0.0634117</v>
+        <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>229.975</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>0.341373</v>
+        <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>475.728</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>1.63303</v>
+        <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>286.951</v>
+        <v>89.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>-0.512806</v>
+        <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>191.845</v>
+        <v>75.48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>3.52664</v>
+        <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>362.638</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>0.988197</v>
+        <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>563.093</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>2.50753</v>
+        <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>369.584</v>
+        <v>84.66</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>1.50229</v>
+        <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>225.188</v>
+        <v>84.66</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>-2.68328</v>
+        <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>357.435</v>
+        <v>59.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>1.4008</v>
+        <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>428.095</v>
+        <v>88.73999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>1.34369</v>
+        <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>331.432</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>-0.577511</v>
+        <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>382.781</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>7.26511</v>
+        <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>173.301</v>
+        <v>53.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>5.22018</v>
+        <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>425.75</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>-0.0225067</v>
+        <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>447.745</v>
+        <v>60.18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>1.96811</v>
+        <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>365.031</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>-0.934715</v>
+        <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>380.257</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>-7.75969</v>
+        <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>336.23</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>4.8476</v>
+        <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>309.636</v>
+        <v>41.82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>-0.918865</v>
+        <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>438.12</v>
+        <v>85.68000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>9.09318</v>
+        <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>241.843</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>-2.8104</v>
+        <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>323.371</v>
+        <v>48.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>-3.68067</v>
+        <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>370.278</v>
+        <v>24.48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>-3.18495</v>
+        <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>236.202</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>0.9188770000000001</v>
+        <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>405.258</v>
+        <v>106.59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>0.625858</v>
+        <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>351.695</v>
+        <v>84.66</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>6.38226</v>
+        <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>267.163</v>
+        <v>31.11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>-4.59499</v>
+        <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>314.293</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>-1.64855</v>
+        <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>392.773</v>
+        <v>82.11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>-0.295589</v>
+        <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>425.56</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>-0.546329</v>
+        <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>286.892</v>
+        <v>37.23</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>1.18683</v>
+        <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>295.95</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>-1.01966</v>
+        <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>391.296</v>
+        <v>42.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>2.9872</v>
+        <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>407.632</v>
+        <v>80.58</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>-1.47895</v>
+        <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>236.748</v>
+        <v>37.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>0.339291</v>
+        <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>302.442</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>-2.0702</v>
+        <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>300.826</v>
+        <v>98.43000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>0.949944</v>
+        <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>466.052</v>
+        <v>74.46000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>-0.102367</v>
+        <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>289.015</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>-1.77901</v>
+        <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>281.311</v>
+        <v>103.02</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>-2.36966</v>
+        <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>228.289</v>
+        <v>78.03</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>-3.48184</v>
+        <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>282.431</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>-0.6516189999999999</v>
+        <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>226.818</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>4.60773</v>
+        <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>383.373</v>
+        <v>62.73</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>1.95026</v>
+        <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>356.117</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>2.39212</v>
+        <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>307.806</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>-3.47644</v>
+        <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>208.154</v>
+        <v>80.58</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>5.31672</v>
+        <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>274.673</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>1.40024</v>
+        <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>429.743</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>-2.75972</v>
+        <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>340.894</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>0.634605</v>
+        <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>307.864</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>-2.50848</v>
+        <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>364.614</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>2.5596</v>
+        <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>250.873</v>
+        <v>84.15000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>-1.15942</v>
+        <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>326.915</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>0.560146</v>
+        <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>384.452</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>1.22319</v>
+        <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>425.583</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>1.2444</v>
+        <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>436.789</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>-1.16875</v>
+        <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>271.438</v>
+        <v>90.27</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>-5.90531</v>
+        <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>200.598</v>
+        <v>97.41</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>-4.44606</v>
+        <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>341.847</v>
+        <v>105.06</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>2.11709</v>
+        <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>336.615</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>-0.427902</v>
+        <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>407.62</v>
+        <v>98.94</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>5.48097</v>
+        <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>406.281</v>
+        <v>53.04</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>-3.83545</v>
+        <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>357.122</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>4.10689</v>
+        <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>319.226</v>
+        <v>89.76000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>1.59954</v>
+        <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>354.439</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>1.3715</v>
+        <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>327.248</v>
+        <v>78.54000000000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>-3.15663</v>
+        <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>481.386</v>
+        <v>99.96000000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>-4.40926</v>
+        <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>297.587</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>1.55039</v>
+        <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>267.504</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>-2.24995</v>
+        <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>321.017</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>-3.95449</v>
+        <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>319.526</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>1.69467</v>
+        <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>289.5</v>
+        <v>107.61</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>-3.26992</v>
+        <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>216.967</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>3.85725</v>
+        <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>225.589</v>
+        <v>105.06</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>2.28471</v>
+        <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>245.914</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>2.72391</v>
+        <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>338.809</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>1.79641</v>
+        <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>367.881</v>
+        <v>78.03</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>6.55781</v>
+        <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>323.05</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>-1.06786</v>
+        <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>297.006</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>1.48645</v>
+        <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>399.432</v>
+        <v>57.12</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>-8.892250000000001</v>
+        <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>356.658</v>
+        <v>77.01000000000001</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>3.63289</v>
+        <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>381.422</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>0.183098</v>
+        <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>251.823</v>
+        <v>59.16</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>-5.7455</v>
+        <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>292.466</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>0.849747</v>
+        <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>464.899</v>
+        <v>66.81</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>4.00831</v>
+        <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>301.137</v>
+        <v>94.35000000000001</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>10.6344</v>
+        <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>239.02</v>
+        <v>69.36</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>-0.258213</v>
+        <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>346.157</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>-0.155346</v>
+        <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>425.547</v>
+        <v>74.46000000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>3.92279</v>
+        <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>360.165</v>
+        <v>103.02</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>2.19995</v>
+        <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>286.236</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>-2.27133</v>
+        <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>354.643</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>-1.17254</v>
+        <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>253.565</v>
+        <v>90.78</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>1.33743</v>
+        <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>276.874</v>
+        <v>40.29</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>-2.32748</v>
+        <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>366.733</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>2.31066</v>
+        <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>256.438</v>
+        <v>51</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>0.183403</v>
+        <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>264.382</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>0.494625</v>
+        <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>395.847</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>0.799084</v>
+        <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>282.714</v>
+        <v>53.04</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>1.92826</v>
+        <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>258.711</v>
+        <v>48.45</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>-1.61544</v>
+        <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>315.106</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>-3.70979</v>
+        <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>350.58</v>
+        <v>71.91</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>-2.72684</v>
+        <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>312.575</v>
+        <v>104.04</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>4.40435</v>
+        <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>304.798</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>1.97465</v>
+        <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>359.392</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>2.04618</v>
+        <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>329.586</v>
+        <v>74.46000000000001</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>-1.17473</v>
+        <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>306.406</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>4.45417</v>
+        <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>488.081</v>
+        <v>60.18</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>1.91434</v>
+        <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>225.767</v>
+        <v>37.23</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>2.24007</v>
+        <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>510.404</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>-5.60015</v>
+        <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>154.424</v>
+        <v>31.11</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>-1.39426</v>
+        <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>330.784</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>4.3289</v>
+        <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>340.46</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>-0.273861</v>
+        <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>400.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>5.77213</v>
+        <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>329.192</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>1.13402</v>
+        <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>322.814</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>9.516019999999999</v>
+        <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>436.302</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>0.075922</v>
+        <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>308.282</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>-0.367077</v>
+        <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>354.563</v>
+        <v>82.11</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>0.39053</v>
+        <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>317.234</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>-0.867941</v>
+        <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>264.704</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>0.925143</v>
+        <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>249.147</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>3.75255</v>
+        <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>419.659</v>
+        <v>67.32000000000001</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>2.90705</v>
+        <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>205.458</v>
+        <v>92.82000000000001</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>3.16166</v>
+        <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>382.598</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>-2.13211</v>
+        <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>408.662</v>
+        <v>82.11</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>-0.9284480000000001</v>
+        <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>290.676</v>
+        <v>94.35000000000001</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>-4.08659</v>
+        <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>276.622</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>5.14959</v>
+        <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>296.266</v>
+        <v>121.38</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>-3.79504</v>
+        <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>292.128</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>0.995255</v>
+        <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>272.045</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>7.49158</v>
+        <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>403.133</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>1.43291</v>
+        <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>304.405</v>
+        <v>113.73</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>3.64091</v>
+        <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>348.744</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>-0.468554</v>
+        <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>284.452</v>
+        <v>79.56</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>2.04524</v>
+        <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>312.449</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>2.43727</v>
+        <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>360.007</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>-1.25515</v>
+        <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>378.044</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>2.43639</v>
+        <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>360.312</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>3.15173</v>
+        <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>305.514</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>1.39485</v>
+        <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>308.136</v>
+        <v>52.53</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>-0.952675</v>
+        <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>361.607</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>-1.16416</v>
+        <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>357.184</v>
+        <v>75.98999999999999</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>-1.04739</v>
+        <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>377.931</v>
+        <v>65.79000000000001</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>-1.83504</v>
+        <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>216.418</v>
+        <v>102.51</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>-1.12168</v>
+        <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>287.446</v>
+        <v>31.11</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>4.59864</v>
+        <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>352.403</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>2.22905</v>
+        <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>449.936</v>
+        <v>72.42</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>-2.768</v>
+        <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>363.912</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>1.93947</v>
+        <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>288.066</v>
+        <v>92.82000000000001</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>2.67364</v>
+        <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>301.709</v>
+        <v>75.98999999999999</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>-5.38315</v>
+        <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>320.676</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>-1.18835</v>
+        <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>369.627</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>-1.41514</v>
+        <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>290.815</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>-4.09906</v>
+        <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>385.882</v>
+        <v>73.44</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>-2.47136</v>
+        <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>283.456</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>3.19215</v>
+        <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>273.311</v>
+        <v>106.08</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>-0.698404</v>
+        <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>324.141</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>2.24877</v>
+        <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>257.918</v>
+        <v>28.56</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>0.422434</v>
+        <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>315.785</v>
+        <v>80.07000000000001</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>3.1108</v>
+        <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>332.772</v>
+        <v>84.15000000000001</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>0.0894794</v>
+        <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>254.247</v>
+        <v>94.35000000000001</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>0.532839</v>
+        <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>359.766</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>-1.31883</v>
+        <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>292.788</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>-4.72219</v>
+        <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>230.041</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>-1.95619</v>
+        <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>335.258</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>-2.61416</v>
+        <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>408.852</v>
+        <v>108.12</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>1.46965</v>
+        <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>315.78</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>3.19247</v>
+        <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>348.326</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>-2.64968</v>
+        <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>382.387</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>2.08219</v>
+        <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>267.379</v>
+        <v>78.03</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>3.14434</v>
+        <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>210.838</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>2.78012</v>
+        <v>193</v>
       </c>
       <c r="B195" t="n">
-        <v>341.246</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>-0.307566</v>
+        <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>372.949</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>3.18678</v>
+        <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>357.217</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>2.1333</v>
+        <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>254.43</v>
+        <v>34.17</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>0.545719</v>
+        <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>378.533</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>-3.87681</v>
+        <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>389.262</v>
+        <v>62.22</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>-0.93852</v>
+        <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>198.546</v>
+        <v>89.76000000000001</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>-1.61992</v>
+        <v>200</v>
       </c>
       <c r="B202" t="n">
-        <v>333.855</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>-4.52148</v>
+        <v>201</v>
       </c>
       <c r="B203" t="n">
-        <v>454.812</v>
+        <v>74.46000000000001</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>4.37763</v>
+        <v>202</v>
       </c>
       <c r="B204" t="n">
-        <v>293.571</v>
+        <v>62.73</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>1.90219</v>
+        <v>203</v>
       </c>
       <c r="B205" t="n">
-        <v>232.302</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>-0.286393</v>
+        <v>204</v>
       </c>
       <c r="B206" t="n">
-        <v>390.564</v>
+        <v>119.85</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>-1.38825</v>
+        <v>205</v>
       </c>
       <c r="B207" t="n">
-        <v>309.244</v>
+        <v>60.69</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>1.68844</v>
+        <v>206</v>
       </c>
       <c r="B208" t="n">
-        <v>276.63</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>-1.65701</v>
+        <v>207</v>
       </c>
       <c r="B209" t="n">
-        <v>327.363</v>
+        <v>120.87</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>2.99698</v>
+        <v>208</v>
       </c>
       <c r="B210" t="n">
-        <v>206.128</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>-3.76898</v>
+        <v>209</v>
       </c>
       <c r="B211" t="n">
-        <v>462.889</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>3.74329</v>
+        <v>210</v>
       </c>
       <c r="B212" t="n">
-        <v>283.003</v>
+        <v>62.73</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>5.27575</v>
+        <v>211</v>
       </c>
       <c r="B213" t="n">
-        <v>282.964</v>
+        <v>41.82</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>4.31777</v>
+        <v>212</v>
       </c>
       <c r="B214" t="n">
-        <v>311.288</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>0.457423</v>
+        <v>213</v>
       </c>
       <c r="B215" t="n">
-        <v>345.057</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>3.19073</v>
+        <v>214</v>
       </c>
       <c r="B216" t="n">
-        <v>188.896</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>-0.866829</v>
+        <v>215</v>
       </c>
       <c r="B217" t="n">
-        <v>382.232</v>
+        <v>71.91</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>-0.179287</v>
+        <v>216</v>
       </c>
       <c r="B218" t="n">
-        <v>288.587</v>
+        <v>83.13</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>-2.92311</v>
+        <v>217</v>
       </c>
       <c r="B219" t="n">
-        <v>361.346</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>-0.988907</v>
+        <v>218</v>
       </c>
       <c r="B220" t="n">
-        <v>288.601</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>0.280607</v>
+        <v>219</v>
       </c>
       <c r="B221" t="n">
-        <v>306.442</v>
+        <v>85.17</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>1.67431</v>
+        <v>220</v>
       </c>
       <c r="B222" t="n">
-        <v>267.14</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>1.95198</v>
+        <v>221</v>
       </c>
       <c r="B223" t="n">
-        <v>304.238</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>-3.03187</v>
+        <v>222</v>
       </c>
       <c r="B224" t="n">
-        <v>272.932</v>
+        <v>67.32000000000001</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>1.26739</v>
+        <v>223</v>
       </c>
       <c r="B225" t="n">
-        <v>254.357</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>-1.29435</v>
+        <v>224</v>
       </c>
       <c r="B226" t="n">
-        <v>314.801</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>1.86066</v>
+        <v>225</v>
       </c>
       <c r="B227" t="n">
-        <v>281.242</v>
+        <v>60.69</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>1.62336</v>
+        <v>226</v>
       </c>
       <c r="B228" t="n">
-        <v>328.934</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>-3.10211</v>
+        <v>227</v>
       </c>
       <c r="B229" t="n">
-        <v>267.185</v>
+        <v>82.11</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>-2.84474</v>
+        <v>228</v>
       </c>
       <c r="B230" t="n">
-        <v>267.564</v>
+        <v>110.67</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>-2.49182</v>
+        <v>229</v>
       </c>
       <c r="B231" t="n">
-        <v>334.295</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>-8.18103</v>
+        <v>230</v>
       </c>
       <c r="B232" t="n">
-        <v>329.964</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>-1.94182</v>
+        <v>231</v>
       </c>
       <c r="B233" t="n">
-        <v>275.563</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>1.08434</v>
+        <v>232</v>
       </c>
       <c r="B234" t="n">
-        <v>231.713</v>
+        <v>72.42</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>0.378191</v>
+        <v>233</v>
       </c>
       <c r="B235" t="n">
-        <v>397.515</v>
+        <v>79.56</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>-0.783791</v>
+        <v>234</v>
       </c>
       <c r="B236" t="n">
-        <v>338.185</v>
+        <v>85.68000000000001</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>4.94805</v>
+        <v>235</v>
       </c>
       <c r="B237" t="n">
-        <v>311.705</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>-3.9151</v>
+        <v>236</v>
       </c>
       <c r="B238" t="n">
-        <v>381.839</v>
+        <v>113.22</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>-4.05175</v>
+        <v>237</v>
       </c>
       <c r="B239" t="n">
-        <v>352.618</v>
+        <v>80.58</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>4.58098</v>
+        <v>238</v>
       </c>
       <c r="B240" t="n">
-        <v>323.942</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>-3.90274</v>
+        <v>239</v>
       </c>
       <c r="B241" t="n">
-        <v>336.287</v>
+        <v>95.37</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>3.89226</v>
+        <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>358.181</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>3.74213</v>
+        <v>241</v>
       </c>
       <c r="B243" t="n">
-        <v>256.008</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>-1.38317</v>
+        <v>242</v>
       </c>
       <c r="B244" t="n">
-        <v>303.497</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>-2.74317</v>
+        <v>243</v>
       </c>
       <c r="B245" t="n">
-        <v>238.384</v>
+        <v>80.58</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>4.19741</v>
+        <v>244</v>
       </c>
       <c r="B246" t="n">
-        <v>495.271</v>
+        <v>94.35000000000001</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>-1.72038</v>
+        <v>245</v>
       </c>
       <c r="B247" t="n">
-        <v>294.324</v>
+        <v>78.54000000000001</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>1.14656</v>
+        <v>246</v>
       </c>
       <c r="B248" t="n">
-        <v>231.058</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>-0.548806</v>
+        <v>247</v>
       </c>
       <c r="B249" t="n">
-        <v>344.005</v>
+        <v>72.42</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>0.861488</v>
+        <v>248</v>
       </c>
       <c r="B250" t="n">
-        <v>326.265</v>
+        <v>83.64</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>1.88904</v>
+        <v>249</v>
       </c>
       <c r="B251" t="n">
-        <v>247.487</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>6.97733</v>
+        <v>250</v>
       </c>
       <c r="B252" t="n">
-        <v>455.355</v>
+        <v>80.07000000000001</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>6.47032</v>
+        <v>251</v>
       </c>
       <c r="B253" t="n">
-        <v>243.34</v>
+        <v>98.43000000000001</v>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="inlineStr">
-        <is>
-          <t>6.47032.1</t>
-        </is>
+      <c r="A254" s="1" t="n">
+        <v>252</v>
       </c>
       <c r="B254" t="n">
-        <v>243.34</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>-3.09826</v>
+        <v>253</v>
       </c>
       <c r="B255" t="n">
-        <v>326.822</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>2.84447</v>
+        <v>254</v>
       </c>
       <c r="B256" t="n">
-        <v>401.782</v>
+        <v>48.45</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>-4.40605</v>
+        <v>255</v>
       </c>
       <c r="B257" t="n">
-        <v>446.917</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>-8.352130000000001</v>
+        <v>256</v>
       </c>
       <c r="B258" t="n">
-        <v>334.493</v>
+        <v>87.72</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>-0.589194</v>
+        <v>257</v>
       </c>
       <c r="B259" t="n">
-        <v>274.764</v>
+        <v>103.02</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>-4.80214</v>
+        <v>258</v>
       </c>
       <c r="B260" t="n">
-        <v>398.744</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>5.419</v>
+        <v>259</v>
       </c>
       <c r="B261" t="n">
-        <v>239.435</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>1.62081</v>
+        <v>260</v>
       </c>
       <c r="B262" t="n">
-        <v>349.043</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>0.569107</v>
+        <v>261</v>
       </c>
       <c r="B263" t="n">
-        <v>265.821</v>
+        <v>89.25</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>-2.50968</v>
+        <v>262</v>
       </c>
       <c r="B264" t="n">
-        <v>445.853</v>
+        <v>107.61</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>-3.00273</v>
+        <v>263</v>
       </c>
       <c r="B265" t="n">
-        <v>370.742</v>
+        <v>72.93000000000001</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>0.0956993</v>
+        <v>264</v>
       </c>
       <c r="B266" t="n">
-        <v>361.771</v>
+        <v>102.51</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>1.51695</v>
+        <v>265</v>
       </c>
       <c r="B267" t="n">
-        <v>343.187</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>-2.13121</v>
+        <v>266</v>
       </c>
       <c r="B268" t="n">
-        <v>241.544</v>
+        <v>65.79000000000001</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>-2.02148</v>
+        <v>267</v>
       </c>
       <c r="B269" t="n">
-        <v>301.134</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>1.17642</v>
+        <v>268</v>
       </c>
       <c r="B270" t="n">
-        <v>405.058</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>4.16272</v>
+        <v>269</v>
       </c>
       <c r="B271" t="n">
-        <v>273.779</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>-0.889832</v>
+        <v>270</v>
       </c>
       <c r="B272" t="n">
-        <v>226.183</v>
+        <v>80.07000000000001</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>-1.48971</v>
+        <v>271</v>
       </c>
       <c r="B273" t="n">
-        <v>178.753</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>-1.34552</v>
+        <v>272</v>
       </c>
       <c r="B274" t="n">
-        <v>255.01</v>
+        <v>48.45</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>8.430540000000001</v>
+        <v>273</v>
       </c>
       <c r="B275" t="n">
-        <v>223.052</v>
+        <v>70.38</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>-2.17545</v>
+        <v>274</v>
       </c>
       <c r="B276" t="n">
-        <v>402.973</v>
+        <v>87.21000000000001</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>-0.865232</v>
+        <v>275</v>
       </c>
       <c r="B277" t="n">
-        <v>424.746</v>
+        <v>59.16</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>-0.9055879999999999</v>
+        <v>276</v>
       </c>
       <c r="B278" t="n">
-        <v>478.25</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>-3.93294</v>
+        <v>277</v>
       </c>
       <c r="B279" t="n">
-        <v>333.785</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>-0.912202</v>
+        <v>278</v>
       </c>
       <c r="B280" t="n">
-        <v>264.339</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>2.58956</v>
+        <v>279</v>
       </c>
       <c r="B281" t="n">
-        <v>344.687</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>1.13528</v>
+        <v>280</v>
       </c>
       <c r="B282" t="n">
-        <v>378.359</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>3.1887</v>
+        <v>281</v>
       </c>
       <c r="B283" t="n">
-        <v>328.837</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>2.56207</v>
+        <v>282</v>
       </c>
       <c r="B284" t="n">
-        <v>282.02</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>0.8476089999999999</v>
+        <v>283</v>
       </c>
       <c r="B285" t="n">
-        <v>317.05</v>
+        <v>83.64</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>-2.50695</v>
+        <v>284</v>
       </c>
       <c r="B286" t="n">
-        <v>205.507</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>6.05964</v>
+        <v>285</v>
       </c>
       <c r="B287" t="n">
-        <v>417.769</v>
+        <v>77.01000000000001</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>-5.12677</v>
+        <v>286</v>
       </c>
       <c r="B288" t="n">
-        <v>302.622</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>1.89122</v>
+        <v>287</v>
       </c>
       <c r="B289" t="n">
-        <v>357.31</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>-1.82451</v>
+        <v>288</v>
       </c>
       <c r="B290" t="n">
-        <v>351.702</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>2.5184</v>
+        <v>289</v>
       </c>
       <c r="B291" t="n">
-        <v>357.647</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>0.847021</v>
+        <v>290</v>
       </c>
       <c r="B292" t="n">
-        <v>216.14</v>
+        <v>85.17</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>-1.15365</v>
+        <v>291</v>
       </c>
       <c r="B293" t="n">
-        <v>177.212</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>1.22796</v>
+        <v>292</v>
       </c>
       <c r="B294" t="n">
-        <v>293.565</v>
+        <v>51</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>-2.88241</v>
+        <v>293</v>
       </c>
       <c r="B295" t="n">
-        <v>243.417</v>
+        <v>78.54000000000001</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>-0.716309</v>
+        <v>294</v>
       </c>
       <c r="B296" t="n">
-        <v>335.323</v>
+        <v>48.45</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>-0.169249</v>
+        <v>295</v>
       </c>
       <c r="B297" t="n">
-        <v>263.114</v>
+        <v>83.13</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>2.99531</v>
+        <v>296</v>
       </c>
       <c r="B298" t="n">
-        <v>401.948</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>3.56795</v>
+        <v>297</v>
       </c>
       <c r="B299" t="n">
-        <v>413.523</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>1.64167</v>
+        <v>298</v>
       </c>
       <c r="B300" t="n">
-        <v>318.164</v>
+        <v>100.98</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>-0.237346</v>
+        <v>299</v>
       </c>
       <c r="B301" t="n">
-        <v>348.864</v>
+        <v>52.53</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>-3.14639</v>
+        <v>300</v>
       </c>
       <c r="B302" t="n">
-        <v>413.721</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>2.09372</v>
+        <v>301</v>
       </c>
       <c r="B303" t="n">
-        <v>352.828</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>2.91094</v>
+        <v>302</v>
       </c>
       <c r="B304" t="n">
-        <v>303.961</v>
+        <v>111.69</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>-0.299791</v>
+        <v>303</v>
       </c>
       <c r="B305" t="n">
-        <v>216.473</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>2.24539</v>
+        <v>304</v>
       </c>
       <c r="B306" t="n">
-        <v>502.856</v>
+        <v>57.12</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>2.02857</v>
+        <v>305</v>
       </c>
       <c r="B307" t="n">
-        <v>478.01</v>
+        <v>84.15000000000001</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>1.53668</v>
+        <v>306</v>
       </c>
       <c r="B308" t="n">
-        <v>353.735</v>
+        <v>81.09</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>-1.41816</v>
+        <v>307</v>
       </c>
       <c r="B309" t="n">
-        <v>308.68</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>3.53329</v>
+        <v>308</v>
       </c>
       <c r="B310" t="n">
-        <v>308.932</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>7.1542</v>
+        <v>309</v>
       </c>
       <c r="B311" t="n">
-        <v>464.215</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>-0.6292720000000001</v>
+        <v>310</v>
       </c>
       <c r="B312" t="n">
-        <v>288.045</v>
+        <v>90.78</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>2.83297</v>
+        <v>311</v>
       </c>
       <c r="B313" t="n">
-        <v>249.468</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>3.73618</v>
+        <v>312</v>
       </c>
       <c r="B314" t="n">
-        <v>366.113</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
-        <v>-0.596633</v>
+        <v>313</v>
       </c>
       <c r="B315" t="n">
-        <v>243.765</v>
+        <v>17.85</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
-        <v>3.86477</v>
+        <v>314</v>
       </c>
       <c r="B316" t="n">
-        <v>313.658</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>2.74713</v>
+        <v>315</v>
       </c>
       <c r="B317" t="n">
-        <v>314.311</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>-4.44214</v>
+        <v>316</v>
       </c>
       <c r="B318" t="n">
-        <v>278.098</v>
+        <v>92.82000000000001</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>3.92699</v>
+        <v>317</v>
       </c>
       <c r="B319" t="n">
-        <v>243.268</v>
+        <v>105.06</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
-        <v>-0.659784</v>
+        <v>318</v>
       </c>
       <c r="B320" t="n">
-        <v>301.168</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
-        <v>-5.05322</v>
+        <v>319</v>
       </c>
       <c r="B321" t="n">
-        <v>309.867</v>
+        <v>80.58</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>-2.67634</v>
+        <v>320</v>
       </c>
       <c r="B322" t="n">
-        <v>288.821</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>2.27925</v>
+        <v>321</v>
       </c>
       <c r="B323" t="n">
-        <v>329.071</v>
+        <v>37.23</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>3.24953</v>
+        <v>322</v>
       </c>
       <c r="B324" t="n">
-        <v>367.869</v>
+        <v>89.25</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>3.76665</v>
+        <v>323</v>
       </c>
       <c r="B325" t="n">
-        <v>263.525</v>
+        <v>62.73</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
-        <v>1.70428</v>
+        <v>324</v>
       </c>
       <c r="B326" t="n">
-        <v>366.355</v>
+        <v>72.42</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
-        <v>-2.19785</v>
+        <v>325</v>
       </c>
       <c r="B327" t="n">
-        <v>290.612</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
-        <v>1.44037</v>
+        <v>326</v>
       </c>
       <c r="B328" t="n">
-        <v>244.047</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
-        <v>-4.25766</v>
+        <v>327</v>
       </c>
       <c r="B329" t="n">
-        <v>277.398</v>
+        <v>82.11</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
-        <v>0.189056</v>
+        <v>328</v>
       </c>
       <c r="B330" t="n">
-        <v>348.008</v>
+        <v>62.73</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
-        <v>0.444561</v>
+        <v>329</v>
       </c>
       <c r="B331" t="n">
-        <v>321.27</v>
+        <v>59.16</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
-        <v>8.50994</v>
+        <v>330</v>
       </c>
       <c r="B332" t="n">
-        <v>341.024</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
-        <v>3.31152</v>
+        <v>331</v>
       </c>
       <c r="B333" t="n">
-        <v>143.147</v>
+        <v>83.64</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
-        <v>-3.22298</v>
+        <v>332</v>
       </c>
       <c r="B334" t="n">
-        <v>349.189</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
-        <v>-5.17773</v>
+        <v>333</v>
       </c>
       <c r="B335" t="n">
-        <v>359.274</v>
+        <v>65.28</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
-        <v>-1.30475</v>
+        <v>334</v>
       </c>
       <c r="B336" t="n">
-        <v>282.273</v>
+        <v>96.39</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
-        <v>-0.95533</v>
+        <v>335</v>
       </c>
       <c r="B337" t="n">
-        <v>329.453</v>
+        <v>62.22</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
-        <v>7.14907</v>
+        <v>336</v>
       </c>
       <c r="B338" t="n">
-        <v>344.455</v>
+        <v>103.53</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
-        <v>1.66329</v>
+        <v>337</v>
       </c>
       <c r="B339" t="n">
-        <v>249.87</v>
+        <v>134.64</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
-        <v>-2.64912</v>
+        <v>338</v>
       </c>
       <c r="B340" t="n">
-        <v>348.42</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
-        <v>-7.85674</v>
+        <v>339</v>
       </c>
       <c r="B341" t="n">
-        <v>261.088</v>
+        <v>89.25</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
-        <v>-5.32423</v>
+        <v>340</v>
       </c>
       <c r="B342" t="n">
-        <v>215.675</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
-        <v>-1.463</v>
+        <v>341</v>
       </c>
       <c r="B343" t="n">
-        <v>347.592</v>
+        <v>83.64</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
-        <v>2.06892</v>
+        <v>342</v>
       </c>
       <c r="B344" t="n">
-        <v>314.044</v>
+        <v>95.37</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
-        <v>0.378143</v>
+        <v>343</v>
       </c>
       <c r="B345" t="n">
-        <v>319.708</v>
+        <v>34.17</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
-        <v>1.08312</v>
+        <v>344</v>
       </c>
       <c r="B346" t="n">
-        <v>463.347</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
-        <v>-0.677944</v>
+        <v>345</v>
       </c>
       <c r="B347" t="n">
-        <v>218.887</v>
+        <v>98.94</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
-        <v>-5.52328</v>
+        <v>346</v>
       </c>
       <c r="B348" t="n">
-        <v>238.594</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
-        <v>-4.6101</v>
+        <v>347</v>
       </c>
       <c r="B349" t="n">
-        <v>309.212</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
-        <v>-0.107033</v>
+        <v>348</v>
       </c>
       <c r="B350" t="n">
-        <v>314.905</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
-        <v>6.73736</v>
+        <v>349</v>
       </c>
       <c r="B351" t="n">
-        <v>267.686</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
-        <v>0.484226</v>
+        <v>350</v>
       </c>
       <c r="B352" t="n">
-        <v>158.616</v>
+        <v>40.29</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
-        <v>-0.324028</v>
+        <v>351</v>
       </c>
       <c r="B353" t="n">
-        <v>329.657</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
-        <v>-3.69337</v>
+        <v>352</v>
       </c>
       <c r="B354" t="n">
-        <v>294.488</v>
+        <v>78.54000000000001</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
-        <v>-2.95259</v>
+        <v>353</v>
       </c>
       <c r="B355" t="n">
-        <v>240.875</v>
+        <v>84.66</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
-        <v>-0.907467</v>
+        <v>354</v>
       </c>
       <c r="B356" t="n">
-        <v>278.825</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
-        <v>4.53773</v>
+        <v>355</v>
       </c>
       <c r="B357" t="n">
-        <v>308.685</v>
+        <v>96.39</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
-        <v>2.80534</v>
+        <v>356</v>
       </c>
       <c r="B358" t="n">
-        <v>398.432</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
-        <v>-4.21008</v>
+        <v>357</v>
       </c>
       <c r="B359" t="n">
-        <v>409.224</v>
+        <v>22.44</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
-        <v>-1.70571</v>
+        <v>358</v>
       </c>
       <c r="B360" t="n">
-        <v>500.064</v>
+        <v>57.12</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
-        <v>5.88444</v>
+        <v>359</v>
       </c>
       <c r="B361" t="n">
-        <v>346.013</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
-        <v>-1.20065</v>
+        <v>360</v>
       </c>
       <c r="B362" t="n">
-        <v>316.924</v>
+        <v>71.91</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
-        <v>-4.51737</v>
+        <v>361</v>
       </c>
       <c r="B363" t="n">
-        <v>323.801</v>
+        <v>60.18</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
-        <v>-0.965462</v>
+        <v>362</v>
       </c>
       <c r="B364" t="n">
-        <v>400.338</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
-        <v>-5.17859</v>
+        <v>363</v>
       </c>
       <c r="B365" t="n">
-        <v>183.685</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
-        <v>0.644173</v>
+        <v>364</v>
       </c>
       <c r="B366" t="n">
-        <v>241.481</v>
+        <v>95.88</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
-        <v>0.145432</v>
+        <v>365</v>
       </c>
       <c r="B367" t="n">
-        <v>334.765</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
-        <v>-0.427254</v>
+        <v>366</v>
       </c>
       <c r="B368" t="n">
-        <v>433.973</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
-        <v>-2.05305</v>
+        <v>367</v>
       </c>
       <c r="B369" t="n">
-        <v>270.843</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
-        <v>-1.18662</v>
+        <v>368</v>
       </c>
       <c r="B370" t="n">
-        <v>277.951</v>
+        <v>100.98</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
-        <v>-6.29183</v>
+        <v>369</v>
       </c>
       <c r="B371" t="n">
-        <v>260.074</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
-        <v>-4.25047</v>
+        <v>370</v>
       </c>
       <c r="B372" t="n">
-        <v>232.848</v>
+        <v>101.49</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
-        <v>-1.29316</v>
+        <v>371</v>
       </c>
       <c r="B373" t="n">
-        <v>243.664</v>
+        <v>74.46000000000001</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
-        <v>3.91239</v>
+        <v>372</v>
       </c>
       <c r="B374" t="n">
-        <v>299.347</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
-        <v>-1.08401</v>
+        <v>373</v>
       </c>
       <c r="B375" t="n">
-        <v>311.929</v>
+        <v>93.84</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
-        <v>-0.926968</v>
+        <v>374</v>
       </c>
       <c r="B376" t="n">
-        <v>261.563</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
-        <v>2.99109</v>
+        <v>375</v>
       </c>
       <c r="B377" t="n">
-        <v>329.264</v>
+        <v>92.82000000000001</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
-        <v>0.266285</v>
+        <v>376</v>
       </c>
       <c r="B378" t="n">
-        <v>215.956</v>
+        <v>91.29000000000001</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
-        <v>-0.37817</v>
+        <v>377</v>
       </c>
       <c r="B379" t="n">
-        <v>284.207</v>
+        <v>72.93000000000001</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
-        <v>0.6311</v>
+        <v>378</v>
       </c>
       <c r="B380" t="n">
-        <v>294.127</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
-        <v>0.901447</v>
+        <v>379</v>
       </c>
       <c r="B381" t="n">
-        <v>288.432</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
-        <v>0.790173</v>
+        <v>380</v>
       </c>
       <c r="B382" t="n">
-        <v>312.872</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
-        <v>-5.05199</v>
+        <v>381</v>
       </c>
       <c r="B383" t="n">
-        <v>335.779</v>
+        <v>62.73</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
-        <v>0.519394</v>
+        <v>382</v>
       </c>
       <c r="B384" t="n">
-        <v>370.388</v>
+        <v>62.22</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
-        <v>1.22405</v>
+        <v>383</v>
       </c>
       <c r="B385" t="n">
-        <v>294.705</v>
+        <v>74.46000000000001</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
-        <v>1.26538</v>
+        <v>384</v>
       </c>
       <c r="B386" t="n">
-        <v>312.63</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
-        <v>-4.03942</v>
+        <v>385</v>
       </c>
       <c r="B387" t="n">
-        <v>308.851</v>
+        <v>51</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
-        <v>0.490978</v>
+        <v>386</v>
       </c>
       <c r="B388" t="n">
-        <v>325.513</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
-        <v>3.23081</v>
+        <v>387</v>
       </c>
       <c r="B389" t="n">
-        <v>332.678</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
-        <v>-2.65989</v>
+        <v>388</v>
       </c>
       <c r="B390" t="n">
-        <v>282.948</v>
+        <v>65.79000000000001</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
-        <v>-7.83613</v>
+        <v>389</v>
       </c>
       <c r="B391" t="n">
-        <v>365.253</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
-        <v>1.9149</v>
+        <v>390</v>
       </c>
       <c r="B392" t="n">
-        <v>209.486</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
-        <v>0.452694</v>
+        <v>391</v>
       </c>
       <c r="B393" t="n">
-        <v>275.089</v>
+        <v>80.07000000000001</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
-        <v>-2.46962</v>
+        <v>392</v>
       </c>
       <c r="B394" t="n">
-        <v>319.073</v>
+        <v>78.03</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
-        <v>1.35594</v>
+        <v>393</v>
       </c>
       <c r="B395" t="n">
-        <v>350.457</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
-        <v>-4.78871</v>
+        <v>394</v>
       </c>
       <c r="B396" t="n">
-        <v>368.651</v>
+        <v>95.37</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
-        <v>-2.81215</v>
+        <v>395</v>
       </c>
       <c r="B397" t="n">
-        <v>287.327</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
-        <v>-1.17977</v>
+        <v>396</v>
       </c>
       <c r="B398" t="n">
-        <v>334.219</v>
+        <v>84.15000000000001</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
-        <v>-1.24434</v>
+        <v>397</v>
       </c>
       <c r="B399" t="n">
-        <v>255.966</v>
+        <v>67.32000000000001</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
-        <v>-0.279736</v>
+        <v>398</v>
       </c>
       <c r="B400" t="n">
-        <v>257.357</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
-        <v>0.995968</v>
+        <v>399</v>
       </c>
       <c r="B401" t="n">
-        <v>387.162</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
-        <v>4.47034</v>
+        <v>400</v>
       </c>
       <c r="B402" t="n">
-        <v>236.96</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
-        <v>1.99407</v>
+        <v>401</v>
       </c>
       <c r="B403" t="n">
-        <v>353.979</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
-        <v>2.72101</v>
+        <v>402</v>
       </c>
       <c r="B404" t="n">
-        <v>314.055</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
-        <v>-1.59679</v>
+        <v>403</v>
       </c>
       <c r="B405" t="n">
-        <v>291.304</v>
+        <v>60.18</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
-        <v>0.671902</v>
+        <v>404</v>
       </c>
       <c r="B406" t="n">
-        <v>326.106</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
-        <v>0.651417</v>
+        <v>405</v>
       </c>
       <c r="B407" t="n">
-        <v>284.473</v>
+        <v>72.93000000000001</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
-        <v>-0.261181</v>
+        <v>406</v>
       </c>
       <c r="B408" t="n">
-        <v>214.375</v>
+        <v>59.16</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
-        <v>-0.0748177</v>
+        <v>407</v>
       </c>
       <c r="B409" t="n">
-        <v>210.442</v>
+        <v>82.11</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
-        <v>1.53641</v>
+        <v>408</v>
       </c>
       <c r="B410" t="n">
-        <v>387.733</v>
+        <v>98.43000000000001</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
-        <v>-1.5445</v>
+        <v>409</v>
       </c>
       <c r="B411" t="n">
-        <v>390.145</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
-        <v>2.15069</v>
+        <v>410</v>
       </c>
       <c r="B412" t="n">
-        <v>342.585</v>
+        <v>97.41</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
-        <v>0.264774</v>
+        <v>411</v>
       </c>
       <c r="B413" t="n">
-        <v>381.517</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
-        <v>-3.23375</v>
+        <v>412</v>
       </c>
       <c r="B414" t="n">
-        <v>313.411</v>
+        <v>93.84</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
-        <v>-5.78444</v>
+        <v>413</v>
       </c>
       <c r="B415" t="n">
-        <v>246.542</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="n">
-        <v>1.83762</v>
+        <v>414</v>
       </c>
       <c r="B416" t="n">
-        <v>303.132</v>
+        <v>60.18</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="n">
-        <v>1.29375</v>
+        <v>415</v>
       </c>
       <c r="B417" t="n">
-        <v>227.222</v>
+        <v>91.29000000000001</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="n">
-        <v>0.566624</v>
+        <v>416</v>
       </c>
       <c r="B418" t="n">
-        <v>325.94</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="1" t="n">
-        <v>4.49161</v>
+        <v>417</v>
       </c>
       <c r="B419" t="n">
-        <v>374.681</v>
+        <v>102.51</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="1" t="n">
-        <v>0.312672</v>
+        <v>418</v>
       </c>
       <c r="B420" t="n">
-        <v>287.156</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="1" t="n">
-        <v>-2.04148</v>
+        <v>419</v>
       </c>
       <c r="B421" t="n">
-        <v>312.711</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="n">
-        <v>-1.55025</v>
+        <v>420</v>
       </c>
       <c r="B422" t="n">
-        <v>295.273</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="n">
-        <v>-1.07982</v>
+        <v>421</v>
       </c>
       <c r="B423" t="n">
-        <v>372.665</v>
+        <v>82.11</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="1" t="n">
-        <v>-2.41297</v>
+        <v>422</v>
       </c>
       <c r="B424" t="n">
-        <v>372.415</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="n">
-        <v>2.65923</v>
+        <v>423</v>
       </c>
       <c r="B425" t="n">
-        <v>352.493</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="n">
-        <v>0.258518</v>
+        <v>424</v>
       </c>
       <c r="B426" t="n">
-        <v>429.166</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="1" t="n">
-        <v>2.39952</v>
+        <v>425</v>
       </c>
       <c r="B427" t="n">
-        <v>257.061</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="n">
-        <v>2.84061</v>
+        <v>426</v>
       </c>
       <c r="B428" t="n">
-        <v>365.629</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="1" t="n">
-        <v>2.94772</v>
+        <v>427</v>
       </c>
       <c r="B429" t="n">
-        <v>339.735</v>
+        <v>77.01000000000001</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="1" t="n">
-        <v>3.52103</v>
+        <v>428</v>
       </c>
       <c r="B430" t="n">
-        <v>371.773</v>
+        <v>75.48</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="1" t="n">
-        <v>1.47358</v>
+        <v>429</v>
       </c>
       <c r="B431" t="n">
-        <v>295.947</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="1" t="n">
-        <v>-0.167301</v>
+        <v>430</v>
       </c>
       <c r="B432" t="n">
-        <v>322.444</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="n">
-        <v>-0.741177</v>
+        <v>431</v>
       </c>
       <c r="B433" t="n">
-        <v>314.774</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="1" t="n">
-        <v>0.946636</v>
+        <v>432</v>
       </c>
       <c r="B434" t="n">
-        <v>342.434</v>
+        <v>94.35000000000001</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="1" t="n">
-        <v>1.75687</v>
+        <v>433</v>
       </c>
       <c r="B435" t="n">
-        <v>364.668</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="1" t="n">
-        <v>-0.82156</v>
+        <v>434</v>
       </c>
       <c r="B436" t="n">
-        <v>291.027</v>
+        <v>99.96000000000001</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
-        <v>1.05193</v>
+        <v>435</v>
       </c>
       <c r="B437" t="n">
-        <v>373.713</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="1" t="n">
-        <v>3.40907</v>
+        <v>436</v>
       </c>
       <c r="B438" t="n">
-        <v>308.243</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="n">
-        <v>-2.06859</v>
+        <v>437</v>
       </c>
       <c r="B439" t="n">
-        <v>382.236</v>
+        <v>94.35000000000001</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="n">
-        <v>-4.95715</v>
+        <v>438</v>
       </c>
       <c r="B440" t="n">
-        <v>270.152</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="n">
-        <v>2.11531</v>
+        <v>439</v>
       </c>
       <c r="B441" t="n">
-        <v>239.992</v>
+        <v>85.17</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="1" t="n">
-        <v>2.16744</v>
+        <v>440</v>
       </c>
       <c r="B442" t="n">
-        <v>378.934</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="n">
-        <v>1.20094</v>
+        <v>441</v>
       </c>
       <c r="B443" t="n">
-        <v>249.423</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="n">
-        <v>0.552273</v>
+        <v>442</v>
       </c>
       <c r="B444" t="n">
-        <v>534.809</v>
+        <v>34.17</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="1" t="n">
-        <v>0.0176506</v>
+        <v>443</v>
       </c>
       <c r="B445" t="n">
-        <v>281.047</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="1" t="n">
-        <v>-1.47535</v>
+        <v>444</v>
       </c>
       <c r="B446" t="n">
-        <v>281.721</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="1" t="n">
-        <v>1.35214</v>
+        <v>445</v>
       </c>
       <c r="B447" t="n">
-        <v>314.838</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="1" t="n">
-        <v>2.06323</v>
+        <v>446</v>
       </c>
       <c r="B448" t="n">
-        <v>259.746</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="1" t="n">
-        <v>-0.0640411</v>
+        <v>447</v>
       </c>
       <c r="B449" t="n">
-        <v>296.973</v>
+        <v>89.76000000000001</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="1" t="n">
-        <v>3.03656</v>
+        <v>448</v>
       </c>
       <c r="B450" t="n">
-        <v>353.236</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="1" t="n">
-        <v>-7.11348</v>
+        <v>449</v>
       </c>
       <c r="B451" t="n">
-        <v>297.049</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="1" t="n">
-        <v>-0.111042</v>
+        <v>450</v>
       </c>
       <c r="B452" t="n">
-        <v>284.932</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="1" t="n">
-        <v>-3.27991</v>
+        <v>451</v>
       </c>
       <c r="B453" t="n">
-        <v>372.372</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="1" t="n">
-        <v>-2.08754</v>
+        <v>452</v>
       </c>
       <c r="B454" t="n">
-        <v>415.116</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="1" t="n">
-        <v>-5.81286</v>
+        <v>453</v>
       </c>
       <c r="B455" t="n">
-        <v>257.608</v>
+        <v>42.33</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="n">
-        <v>-1.39519</v>
+        <v>454</v>
       </c>
       <c r="B456" t="n">
-        <v>278.185</v>
+        <v>59.67</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="1" t="n">
-        <v>2.64856</v>
+        <v>455</v>
       </c>
       <c r="B457" t="n">
-        <v>338.734</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="1" t="n">
-        <v>2.64719</v>
+        <v>456</v>
       </c>
       <c r="B458" t="n">
-        <v>337.954</v>
+        <v>32.64</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="1" t="n">
-        <v>1.25607</v>
+        <v>457</v>
       </c>
       <c r="B459" t="n">
-        <v>411.974</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="1" t="n">
-        <v>3.99554</v>
+        <v>458</v>
       </c>
       <c r="B460" t="n">
-        <v>399.424</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="1" t="n">
-        <v>4.31059</v>
+        <v>459</v>
       </c>
       <c r="B461" t="n">
-        <v>190.733</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="1" t="n">
-        <v>1.0666</v>
+        <v>460</v>
       </c>
       <c r="B462" t="n">
-        <v>300.392</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="1" t="n">
-        <v>3.6438</v>
+        <v>461</v>
       </c>
       <c r="B463" t="n">
-        <v>341.88</v>
+        <v>78.54000000000001</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="1" t="n">
-        <v>-2.69572</v>
+        <v>462</v>
       </c>
       <c r="B464" t="n">
-        <v>210.873</v>
+        <v>85.17</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="1" t="n">
-        <v>-3.5386</v>
+        <v>463</v>
       </c>
       <c r="B465" t="n">
-        <v>344.876</v>
+        <v>72.93000000000001</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="1" t="n">
-        <v>2.07226</v>
+        <v>464</v>
       </c>
       <c r="B466" t="n">
-        <v>263.951</v>
+        <v>60.18</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="1" t="n">
-        <v>-3.06616</v>
+        <v>465</v>
       </c>
       <c r="B467" t="n">
-        <v>438.918</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="1" t="n">
-        <v>1.04817</v>
+        <v>466</v>
       </c>
       <c r="B468" t="n">
-        <v>264.575</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="1" t="n">
-        <v>1.6933</v>
+        <v>467</v>
       </c>
       <c r="B469" t="n">
-        <v>270.363</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="1" t="n">
-        <v>4.39407</v>
+        <v>468</v>
       </c>
       <c r="B470" t="n">
-        <v>274.91</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="1" t="n">
-        <v>2.15487</v>
+        <v>469</v>
       </c>
       <c r="B471" t="n">
-        <v>355.498</v>
+        <v>98.43000000000001</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="1" t="n">
-        <v>-5.13338</v>
+        <v>470</v>
       </c>
       <c r="B472" t="n">
-        <v>256.914</v>
+        <v>75.48</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="1" t="n">
-        <v>2.00408</v>
+        <v>471</v>
       </c>
       <c r="B473" t="n">
-        <v>294.417</v>
+        <v>100.98</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="1" t="n">
-        <v>-3.32473</v>
+        <v>472</v>
       </c>
       <c r="B474" t="n">
-        <v>320.187</v>
+        <v>77.01000000000001</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="n">
-        <v>1.15191</v>
+        <v>473</v>
       </c>
       <c r="B475" t="n">
-        <v>290.391</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="1" t="n">
-        <v>0.707508</v>
+        <v>474</v>
       </c>
       <c r="B476" t="n">
-        <v>302.566</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="1" t="n">
-        <v>-5.63005</v>
+        <v>475</v>
       </c>
       <c r="B477" t="n">
-        <v>261.849</v>
+        <v>32.64</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="1" t="n">
-        <v>0.014679</v>
+        <v>476</v>
       </c>
       <c r="B478" t="n">
-        <v>373.531</v>
+        <v>98.43000000000001</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="1" t="n">
-        <v>2.70513</v>
+        <v>477</v>
       </c>
       <c r="B479" t="n">
-        <v>223.018</v>
+        <v>67.32000000000001</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="1" t="n">
-        <v>-1.99981</v>
+        <v>478</v>
       </c>
       <c r="B480" t="n">
-        <v>418.728</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="1" t="n">
-        <v>1.04874</v>
+        <v>479</v>
       </c>
       <c r="B481" t="n">
-        <v>364.692</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="1" t="n">
-        <v>2.11892</v>
+        <v>480</v>
       </c>
       <c r="B482" t="n">
-        <v>304.267</v>
+        <v>13.26</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="1" t="n">
-        <v>-2.94925</v>
+        <v>481</v>
       </c>
       <c r="B483" t="n">
-        <v>160.676</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="1" t="n">
-        <v>2.13603</v>
+        <v>482</v>
       </c>
       <c r="B484" t="n">
-        <v>280.968</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="1" t="n">
-        <v>5.90285</v>
+        <v>483</v>
       </c>
       <c r="B485" t="n">
-        <v>445.507</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="1" t="n">
-        <v>5.11987</v>
+        <v>484</v>
       </c>
       <c r="B486" t="n">
-        <v>242.645</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="1" t="n">
-        <v>-0.567589</v>
+        <v>485</v>
       </c>
       <c r="B487" t="n">
-        <v>322.196</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="1" t="n">
-        <v>-2.42413</v>
+        <v>486</v>
       </c>
       <c r="B488" t="n">
-        <v>280.772</v>
+        <v>73.44</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="1" t="n">
-        <v>4.20514</v>
+        <v>487</v>
       </c>
       <c r="B489" t="n">
-        <v>422.583</v>
+        <v>125.97</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="1" t="n">
-        <v>-2.969</v>
+        <v>488</v>
       </c>
       <c r="B490" t="n">
-        <v>214.048</v>
+        <v>90.27</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="1" t="n">
-        <v>-1.10227</v>
+        <v>489</v>
       </c>
       <c r="B491" t="n">
-        <v>362.907</v>
+        <v>66.81</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="1" t="n">
-        <v>3.60322</v>
+        <v>490</v>
       </c>
       <c r="B492" t="n">
-        <v>315.899</v>
+        <v>89.76000000000001</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="1" t="n">
-        <v>-2.57798</v>
+        <v>491</v>
       </c>
       <c r="B493" t="n">
-        <v>282.236</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="1" t="n">
-        <v>1.02894</v>
+        <v>492</v>
       </c>
       <c r="B494" t="n">
-        <v>401.127</v>
+        <v>60.18</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="1" t="n">
-        <v>0.324059</v>
+        <v>493</v>
       </c>
       <c r="B495" t="n">
-        <v>188.684</v>
+        <v>65.28</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="1" t="n">
-        <v>-4.11098</v>
+        <v>494</v>
       </c>
       <c r="B496" t="n">
-        <v>319.11</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="1" t="n">
-        <v>-0.538471</v>
+        <v>495</v>
       </c>
       <c r="B497" t="n">
-        <v>331.259</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="1" t="n">
-        <v>-1.7797</v>
+        <v>496</v>
       </c>
       <c r="B498" t="n">
-        <v>323.7</v>
+        <v>69.36</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="1" t="n">
-        <v>0.252533</v>
+        <v>497</v>
       </c>
       <c r="B499" t="n">
-        <v>386.022</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="1" t="n">
-        <v>4.56938</v>
+        <v>498</v>
       </c>
       <c r="B500" t="n">
-        <v>226.424</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="1" t="n">
-        <v>7.24482</v>
+        <v>499</v>
       </c>
       <c r="B501" t="n">
-        <v>332.984</v>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" s="1" t="n">
-        <v>-4.87334</v>
-      </c>
-      <c r="B502" t="n">
-        <v>427.421</v>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" s="1" t="n">
-        <v>-3.3765</v>
-      </c>
-      <c r="B503" t="n">
-        <v>238.498</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" s="1" t="n">
-        <v>1.74009</v>
-      </c>
-      <c r="B504" t="n">
-        <v>314.357</v>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" s="1" t="n">
-        <v>-4.38238</v>
-      </c>
-      <c r="B505" t="n">
-        <v>250.569</v>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" s="1" t="n">
-        <v>3.76867</v>
-      </c>
-      <c r="B506" t="n">
-        <v>309.976</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" s="1" t="n">
-        <v>3.29538</v>
-      </c>
-      <c r="B507" t="n">
-        <v>273.827</v>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" s="1" t="n">
-        <v>1.38256</v>
-      </c>
-      <c r="B508" t="n">
-        <v>247.728</v>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" s="1" t="n">
-        <v>-2.10703</v>
-      </c>
-      <c r="B509" t="n">
-        <v>342.111</v>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" s="1" t="n">
-        <v>4.2636</v>
-      </c>
-      <c r="B510" t="n">
-        <v>300.293</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" s="1" t="n">
-        <v>-1.22491</v>
-      </c>
-      <c r="B511" t="n">
-        <v>413.888</v>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" s="1" t="n">
-        <v>-2.75333</v>
-      </c>
-      <c r="B512" t="n">
-        <v>340.412</v>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" s="1" t="n">
-        <v>-0.488895</v>
-      </c>
-      <c r="B513" t="n">
-        <v>373.958</v>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" s="1" t="n">
-        <v>-0.644768</v>
-      </c>
-      <c r="B514" t="n">
-        <v>322.76</v>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" s="1" t="n">
-        <v>4.227</v>
-      </c>
-      <c r="B515" t="n">
-        <v>353.298</v>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" s="1" t="n">
-        <v>0.284317</v>
-      </c>
-      <c r="B516" t="n">
-        <v>320.469</v>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" s="1" t="n">
-        <v>-1.04306</v>
-      </c>
-      <c r="B517" t="n">
-        <v>269.152</v>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" s="1" t="n">
-        <v>-2.92252</v>
-      </c>
-      <c r="B518" t="n">
-        <v>311.067</v>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" s="1" t="n">
-        <v>-0.525181</v>
-      </c>
-      <c r="B519" t="n">
-        <v>308.994</v>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" s="1" t="n">
-        <v>3.85701</v>
-      </c>
-      <c r="B520" t="n">
-        <v>286.596</v>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" s="1" t="n">
-        <v>-5.68861</v>
-      </c>
-      <c r="B521" t="n">
-        <v>240.657</v>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" s="1" t="n">
-        <v>-3.32717</v>
-      </c>
-      <c r="B522" t="n">
-        <v>375.667</v>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" s="1" t="n">
-        <v>0.119492</v>
-      </c>
-      <c r="B523" t="n">
-        <v>277.182</v>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" s="1" t="n">
-        <v>-0.9328959999999999</v>
-      </c>
-      <c r="B524" t="n">
-        <v>243.764</v>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" s="1" t="n">
-        <v>2.07619</v>
-      </c>
-      <c r="B525" t="n">
-        <v>318.934</v>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" s="1" t="n">
-        <v>2.08943</v>
-      </c>
-      <c r="B526" t="n">
-        <v>200.52</v>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" s="1" t="n">
-        <v>-2.61505</v>
-      </c>
-      <c r="B527" t="n">
-        <v>245.073</v>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" s="1" t="n">
-        <v>1.29231</v>
-      </c>
-      <c r="B528" t="n">
-        <v>354.803</v>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" s="1" t="n">
-        <v>-3.08839</v>
-      </c>
-      <c r="B529" t="n">
-        <v>251.939</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" s="1" t="n">
-        <v>-3.2774</v>
-      </c>
-      <c r="B530" t="n">
-        <v>271.48</v>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" s="1" t="n">
-        <v>-0.435101</v>
-      </c>
-      <c r="B531" t="n">
-        <v>233.718</v>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" s="1" t="n">
-        <v>0.192051</v>
-      </c>
-      <c r="B532" t="n">
-        <v>258.76</v>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" s="1" t="n">
-        <v>-2.79299</v>
-      </c>
-      <c r="B533" t="n">
-        <v>373.348</v>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" s="1" t="n">
-        <v>-0.0477943</v>
-      </c>
-      <c r="B534" t="n">
-        <v>278.388</v>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" s="1" t="n">
-        <v>-2.46238</v>
-      </c>
-      <c r="B535" t="n">
-        <v>269.656</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" s="1" t="n">
-        <v>4.67256</v>
-      </c>
-      <c r="B536" t="n">
-        <v>270.504</v>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" s="1" t="n">
-        <v>-1.04088</v>
-      </c>
-      <c r="B537" t="n">
-        <v>335.639</v>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" s="1" t="n">
-        <v>-1.51572</v>
-      </c>
-      <c r="B538" t="n">
-        <v>411.583</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" s="1" t="n">
-        <v>-4.77757</v>
-      </c>
-      <c r="B539" t="n">
-        <v>292.35</v>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" s="1" t="n">
-        <v>0.7594070000000001</v>
-      </c>
-      <c r="B540" t="n">
-        <v>310.278</v>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" s="1" t="n">
-        <v>-0.524513</v>
-      </c>
-      <c r="B541" t="n">
-        <v>357.748</v>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" s="1" t="n">
-        <v>-2.73501</v>
-      </c>
-      <c r="B542" t="n">
-        <v>355.552</v>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" s="1" t="n">
-        <v>-4.7107</v>
-      </c>
-      <c r="B543" t="n">
-        <v>287.26</v>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" s="1" t="n">
-        <v>-4.94009</v>
-      </c>
-      <c r="B544" t="n">
-        <v>284.848</v>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" s="1" t="n">
-        <v>-2.34786</v>
-      </c>
-      <c r="B545" t="n">
-        <v>166.068</v>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" s="1" t="n">
-        <v>0.539425</v>
-      </c>
-      <c r="B546" t="n">
-        <v>339.264</v>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" s="1" t="n">
-        <v>4.55172</v>
-      </c>
-      <c r="B547" t="n">
-        <v>261.075</v>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" s="1" t="n">
-        <v>-3.15898</v>
-      </c>
-      <c r="B548" t="n">
-        <v>350.245</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" s="1" t="n">
-        <v>-2.59711</v>
-      </c>
-      <c r="B549" t="n">
-        <v>293.219</v>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" s="1" t="n">
-        <v>1.31528</v>
-      </c>
-      <c r="B550" t="n">
-        <v>474.261</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" s="1" t="n">
-        <v>-6.9049</v>
-      </c>
-      <c r="B551" t="n">
-        <v>281.098</v>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" s="1" t="n">
-        <v>3.16217</v>
-      </c>
-      <c r="B552" t="n">
-        <v>342.101</v>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" s="1" t="n">
-        <v>-1.48765</v>
-      </c>
-      <c r="B553" t="n">
-        <v>289.995</v>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" s="1" t="n">
-        <v>-0.906887</v>
-      </c>
-      <c r="B554" t="n">
-        <v>289.355</v>
+        <v>46.92</v>
       </c>
     </row>
   </sheetData>
